--- a/reports/2026/09/vulns-2026-09-21.xlsx
+++ b/reports/2026/09/vulns-2026-09-21.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T10:23 to 2026-09-21T10:23</t>
+          <t>2026-09-20T10:31 to 2026-09-21T10:31</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:23:32 UTC</t>
+          <t>2026-09-21 10:31:38 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/2026/09/vulns-2026-09-21.xlsx
+++ b/reports/2026/09/vulns-2026-09-21.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20T10:31 to 2026-09-21T10:31</t>
+          <t>2026-09-20T10:33 to 2026-09-21T10:33</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:31:38 UTC</t>
+          <t>2026-09-21 10:33:47 UTC</t>
         </is>
       </c>
     </row>
